--- a/docs/需求记录.xlsx
+++ b/docs/需求记录.xlsx
@@ -514,10 +514,14 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待评估</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 提交 1e6c6d1：年/月/日/时/分下拉 + 省市区县三级联动，12 位速记保留并双向同步</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -543,10 +547,14 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待评估</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 方案见 docs/2026-09-08-需求方案；根因 --metal 与 --earth 同色，庚辛申酉都受影响。待与老师确认要黄色的原因再定改法</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -572,10 +580,14 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待评估</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 提交 9d76dc8：按北京时日期判、24 项都算、每盘自动默认不覆盖手动切换</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -601,10 +613,14 @@
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待评估</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 数据底座已提交 6b4ab3e（1900–2100 节气冻结表，三关验证）；万年历页交 Codex，任务书 docs/2026-09-08-任务书-codex-万年历页.md</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/docs/需求记录.xlsx
+++ b/docs/需求记录.xlsx
@@ -613,12 +613,12 @@
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 数据底座已提交 6b4ab3e（1900–2100 节气冻结表，三关验证）；万年历页交 Codex，任务书 docs/2026-09-08-任务书-codex-万年历页.md</t>
+          <t>2026-09-08 底座 6b4ab3e + 万年历页 e853c34（Codex 实现，回执 docs/reviews/2026-09-08-回执-codex-万年历页.md）</t>
         </is>
       </c>
     </row>

--- a/docs/需求记录.xlsx
+++ b/docs/需求记录.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -622,6 +622,38 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>排盘引擎</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>大运流年（一期，独立需求）：排出起运岁数、十步大运、流年干支；起运口径（足日/时辰）可切换；裁定表单可勾大运分歧。不接老师《地支运算体系》的权重计算，不做岁运引动判定。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>已立项</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-10 Jing 决定放一期。方案待写；先做地支关系标注（PRD-branch-relations v1.1）。预估 3–4 天。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/需求记录.xlsx
+++ b/docs/需求记录.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-10 Jing 决定放一期。方案待写；先做地支关系标注（PRD-branch-relations v1.1）。预估 3–4 天。</t>
+          <t>2026-09-10 Jing 决定放一期。2026-09-11 方案 docs/plans/PRD-luck-cycles.md（待定稿）；引擎 engine/src/luck.js 已实现并与易百查样盘对上，前端与裁定扩展待原型。预估剩 2–3 天。</t>
         </is>
       </c>
     </row>
